--- a/WorkBot/refactor/data/orders/FingerLakes Farms/FingerLakes Farms_Collegetown_2025-10-10.xlsx
+++ b/WorkBot/refactor/data/orders/FingerLakes Farms/FingerLakes Farms_Collegetown_2025-10-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,114 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>80.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>003003</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Red Jacket - Fuji Apple</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>11.25</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>22.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>003004</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Red Jacket - Rasp/Apple</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>11.25</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>22.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>003005</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Red Jacket - Strawberry (12oz)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>11.25</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>22.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>003014</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Red Jacket - Fuji Apple 32oz</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>25.95</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>25.95</t>
         </is>
       </c>
     </row>
